--- a/aanvullijst-beurs-2026-10.xlsx
+++ b/aanvullijst-beurs-2026-10.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lijst" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toelichting" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Weggehaald (al besteld)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Toelichting" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lijst'!$A$1:$C$187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Lijst'!$A$1:$D$107</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -423,12 +424,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C187"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="58" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,6 +449,11 @@
           <t>Qty</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Al besteld (EFS)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -460,7 +467,10 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>12</v>
+        <v>9</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -475,7 +485,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -492,6 +505,7 @@
       <c r="C4" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -505,7 +519,10 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -520,7 +537,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -535,7 +555,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +573,10 @@
         </is>
       </c>
       <c r="C8" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -565,7 +591,10 @@
         </is>
       </c>
       <c r="C9" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -582,6 +611,7 @@
       <c r="C10" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="D10" s="2" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -595,7 +625,10 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -610,2636 +643,1620 @@
         </is>
       </c>
       <c r="C12" s="2" t="n">
-        <v>30</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="D12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MYJ.27023</t>
+          <t>MYJ.27016</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A-Planner Diary 2027 - Beige Linen</t>
+          <t>My Journal Diary 2027 - Checked Blue Chocolate</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MYJ.27024</t>
+          <t>MYJ.27002</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A-Planner Diary 2027 - Pink Linen</t>
+          <t>My Journal Diary 2027 - Floral Dark Blue/Light Blue</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MYJ.27016</t>
+          <t>MYJ.27004</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>My Journal Diary 2027 - Checked Blue Chocolate</t>
+          <t>My Journal Diary 2027 - Chocolate</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MYJ.27002</t>
+          <t>MYJ.27036</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>My Journal Diary 2027 - Floral Dark Blue/Light Blue</t>
+          <t>A-Journal Desk Calendar - Pink Red 2027</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>6</v>
+        <v>33</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MYJ.27004</t>
+          <t>FAB.91220</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>My Journal Diary 2027 - Chocolate</t>
+          <t>Fabrique a la Carte Birthday Calender - Sun</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>6</v>
+        <v>34</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MYJ.27036</t>
+          <t>MYJ.91134</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A-Journal Desk Calendar - Pink Red 2027</t>
+          <t>A-Journal Recipe Journal</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>30</v>
+        <v>5</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FAB.91220</t>
+          <t>MYJ.91136</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fabrique a la Carte Birthday Calender - Sun</t>
+          <t>A-Journal Meal Planner</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>30</v>
+        <v>4</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MYJ.91134</t>
+          <t>MYJ.91135</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A-Journal Recipe Journal</t>
+          <t>A-Journal Notepad Grocery List</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="D20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MYJ.91136</t>
+          <t>MYJ.91140</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A-Journal Meal Planner</t>
+          <t>A-Yatzy - Yahtzee - Blue</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MYJ.91135</t>
+          <t>MYJ.91139</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A-Journal Notepad Grocery List</t>
+          <t>A-Yatzy - Yahtzee - Pink Red</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MYJ.91140</t>
+          <t>FAB.91278</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A-Yatzy - Yahtzee - Blue</t>
+          <t>Fabrique Puzzle Mini - City life</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>MYJ.91139</t>
+          <t>MYJ.91075</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A-Yatzy - Yahtzee - Pink Red</t>
+          <t>A-Journal Playing Cards</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>6</v>
+        <v>32</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FAB.91278</t>
+          <t>FAB.91251</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fabrique Puzzle Mini - City life</t>
+          <t>Fabrique Playing Cards - Summer</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>6</v>
+        <v>33</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MYJ.91075</t>
+          <t>FAB.91252</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A-Journal Playing Cards</t>
+          <t>Fabrique Playing Cards - Winter</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>20</v>
+        <v>33</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FAB.91251</t>
+          <t>MYJ.91157</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fabrique Playing Cards - Summer</t>
+          <t>A-Journal Pen - Golden</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FAB.91252</t>
+          <t>MYJ.91158</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fabrique Playing Cards - Winter</t>
+          <t>A-Journal Pen - Pink Red</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>20</v>
+        <v>28</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MYJ.91157</t>
+          <t>FAB.91209</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A-Journal Pen - Golden</t>
+          <t>Fabrique Deskplanner - Stripes</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>20</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MYJ.91158</t>
+          <t>FAB.91221</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A-Journal Pen - Pink Red</t>
+          <t>Fabrique a la Carte Birthday Calender - Flowers</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>20</v>
+        <v>1</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FAB.91204</t>
+          <t>FAB.91222</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Travel Notes - Travel Diary</t>
+          <t>Fabrique Deskplanner Stripes Yellow</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D31" s="2" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FAB.91209</t>
+          <t>FAB.91223</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fabrique Deskplanner - Stripes</t>
+          <t>Fabrique Notebook Stripes Yellow</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v>2</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FAB.91212</t>
+          <t>FAB.91224</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fabrique Notebook - Happy Flowers</t>
+          <t>Fabrique Notebook Stripes Orange</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D33" s="2" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FAB.91221</t>
+          <t>FAB.91225</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fabrique a la Carte Birthday Calender - Flowers</t>
+          <t>Fabrique Notepad Stripes Blue</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FAB.91222</t>
+          <t>FAB.91226</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fabrique Deskplanner Stripes Yellow</t>
+          <t>Fabrique Notepad Flowers</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D35" s="2" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FAB.91223</t>
+          <t>FAB.91227</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fabrique Notebook Stripes Yellow</t>
+          <t>Fabrique Birthday Calendar - Flora</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FAB.91224</t>
+          <t>FAB.91229</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Fabrique Notebook Stripes Orange</t>
+          <t>Birthday Calendar Sun Pink</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FAB.91225</t>
+          <t>FAB.91230</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Fabrique Notepad Stripes Blue</t>
+          <t>Birthday Calendar Birds</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FAB.91226</t>
+          <t>FAB.91232</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fabrique Notepad Flowers</t>
+          <t>Fabrique Notebook - Stripes Pink</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D39" s="2" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FAB.91227</t>
+          <t>FAB.91234</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fabrique Birthday Calendar - Flora</t>
+          <t>Personal Journal - Palmtree</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FAB.91228</t>
+          <t>FAB.91238</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>One Line a Day Sun</t>
+          <t>Fabrique Birthday Calendar - Palmtree Checkered</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v>1</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FAB.91229</t>
+          <t>FAB.91239</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Birthday Calendar Sun Pink</t>
+          <t>Fabrique Birthday Calendar - Flowers Beige</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FAB.91230</t>
+          <t>FAB.91240</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Birthday Calendar Birds</t>
+          <t>Fabrique Notebook - Palmtree Pink</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FAB.91231</t>
+          <t>FAB.91241</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fabrique Notebook - Sun Beige Lavender</t>
+          <t>Fabrique Notebook - Checkered Palm</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FAB.91232</t>
+          <t>FAB.91243</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fabrique Notebook - Stripes Pink</t>
+          <t>Fabrique Sketchbook A4 Flower</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FAB.91233</t>
+          <t>FAB.91245</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fabrique Notebook - Sun Pink</t>
+          <t>Fabrique A7 Notebook Striped Blue</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="D46" s="2" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FAB.91234</t>
+          <t>FAB.91247</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Personal Journal - Palmtree</t>
+          <t>Fabrique Birthday Calendar - Poppy</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FAB.91237</t>
+          <t>FAB.91248</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fabrique A6 Notebook - Stripes</t>
+          <t>Fabrique Birthday Calendar - Cake</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FAB.91238</t>
+          <t>FAB.91249</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fabrique Birthday Calendar - Palmtree Checkered</t>
+          <t>Birthday Calendar - Altar Sun</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FAB.91239</t>
+          <t>FAB.91254</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fabrique Birthday Calendar - Flowers Beige</t>
+          <t>Fabrique Affirmation Cards</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FAB.91240</t>
+          <t>FAB.91256</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fabrique Notebook - Palmtree Pink</t>
+          <t>Fabrique Notebook Stripes Dark blue</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>FAB.91241</t>
+          <t>FAB.91265</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fabrique Notebook - Checkered Palm</t>
+          <t>Fabrique Notepad A Table</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FAB.91242</t>
+          <t>FAB.91268</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fabrique Sketchbook A4 Sun</t>
+          <t>One line a day Sun Flow Pink</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FAB.91243</t>
+          <t>FAB.91269</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fabrique Sketchbook A4 Flower</t>
+          <t>Fabrique Bullet Journal Sun Flow Lavender</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v>2</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>FAB.91245</t>
+          <t>FAB.91270</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fabrique A7 Notebook Striped Blue</t>
+          <t>Fabrique Notebook Stripes Lavender</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FAB.91247</t>
+          <t>FAB.91271</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fabrique Birthday Calendar - Poppy</t>
+          <t>Fabrique Deskplanner Stripes Pink Red</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D56" s="2" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FAB.91248</t>
+          <t>FAB.91275</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fabrique Birthday Calendar - Cake</t>
+          <t>Fabrique Birthday Calendar - Dogs</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D57" s="2" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FAB.91249</t>
+          <t>FAB.91276</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Birthday Calendar - Altar Sun</t>
+          <t>Fabrique Birthday Calendar - Cats</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D58" s="2" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FAB.91250</t>
+          <t>INK.91033</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Birthday Calendar - Flower Vase</t>
+          <t>&amp;INK One Line A Day Journal - Jungle</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D59" s="2" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FAB.91253</t>
+          <t>MYJ.19008</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fabrique Playing Cards Stripes - Red Pink</t>
+          <t>Notebook - Lilac</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v>2</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FAB.91254</t>
+          <t>MYJ.91029</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fabrique Affirmation Cards</t>
+          <t>A-Journal Address Book</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FAB.91255</t>
+          <t>MYJ.91030</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fabrique Writing Cards</t>
+          <t>Daily Journal</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FAB.91256</t>
+          <t>MYJ.91034</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fabrique Notebook Stripes Dark blue</t>
+          <t>A-Journal Deskplanner - Linen</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FAB.91262</t>
+          <t>MYJ.91045</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fabrique Notepad Paris</t>
+          <t>Writing Paper</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D64" s="2" t="n"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FAB.91264</t>
+          <t>MYJ.91047</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fabrique Meal planner A Table</t>
+          <t>A-Journal Notepad - Blue</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D65" s="2" t="n"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FAB.91265</t>
+          <t>MYJ.91050</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fabrique Notepad A Table</t>
+          <t>Notebook Toile de Jouy</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FAB.91266</t>
+          <t>MYJ.91051</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>One line a day Stripes Pink Red</t>
+          <t>A-Journal Undated Agenda</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FAB.91267</t>
+          <t>MYJ.91052</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Notepad Stripes Pink Red</t>
+          <t>A-Journal Spiral Notebook - A4</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D68" s="2" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FAB.91268</t>
+          <t>MYJ.91059</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>One line a day Sun Flow Pink</t>
+          <t>A-Journal One Line a Day - Flow Mint</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D69" s="2" t="n"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FAB.91269</t>
+          <t>MYJ.91060</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fabrique Bullet Journal Sun Flow Lavender</t>
+          <t>A-Journal Set of 2 Softcover Notebooks - Coral + Lilac</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D70" s="2" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FAB.91270</t>
+          <t>MYJ.91061</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Fabrique Notebook Stripes Lavender</t>
+          <t>A-Journal Notepad - Beige</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FAB.91271</t>
+          <t>MYJ.91064</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Fabrique Deskplanner Stripes Pink Red</t>
+          <t>A-Journal Birthday Calender - Arty</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FAB.91273</t>
+          <t>MYJ.91067</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fabrique Playing Cards - Dogs</t>
+          <t>A-Journal Notebook Groovy - Pink</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>FAB.91274</t>
+          <t>MYJ.91069</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fabrique Playing  Cards - Cats</t>
+          <t>A-Journal Notebook - Flow Mint</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>FAB.91275</t>
+          <t>MYJ.91073</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fabrique Birthday Calendar - Dogs</t>
+          <t>A-Puzzle Pool Party</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>FAB.91276</t>
+          <t>MYJ.91074</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fabrique Birthday Calendar - Cats</t>
+          <t>A-Puzzle Tropical</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>FAB.91277</t>
+          <t>MYJ.91076</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fabrique Puzzle Mini - Dogs+Cats</t>
+          <t>A-Journal Journaling Cards</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>FAB.91279</t>
+          <t>MYJ.91077</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Fabrique Cardset Dogs+Cats</t>
+          <t>A-Journal One Line a Day Checkered</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D78" s="2" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FAB.91280</t>
+          <t>MYJ.91081</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Fabrique Recipe Journal - A Table</t>
+          <t>A-Journal Notebook Terracotta Checkered</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D79" s="2" t="n"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>FAB.91281</t>
+          <t>MYJ.91084</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fabrique Notebook Print Multi</t>
+          <t>A-Journal Affirmation Cards - Daily Affirmations</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D80" s="2" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>FAB.91282</t>
+          <t>MYJ.91087</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fabrique Notebook Flowers Blue</t>
+          <t>A-Journal A6 Notebook - Pink</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>INK.91033</t>
+          <t>MYJ.91088</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>&amp;INK One Line A Day Journal - Jungle</t>
+          <t>A-Journal A6 Notebook - Green Stripes</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D82" s="2" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>MYJ.17002</t>
+          <t>MYJ.91094</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Notebook Journal</t>
+          <t>A-Journal Accordion Folder - Coral</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="D83" s="2" t="n"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>MYJ.17003</t>
+          <t>MYJ.91095</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wedding Journal</t>
+          <t>A-Journal One Line a Day - Linen Emerald</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>MYJ.17004</t>
+          <t>MYJ.91096</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Travel Journal</t>
+          <t>One Line a Day Flow - Blue Brown</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>MYJ.18009</t>
+          <t>MYJ.91097</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>A-Journal Notelets set of 3 notebooks</t>
+          <t>A-Journal Notebook Arty Green</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D86" s="2" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MYJ.19006</t>
+          <t>MYJ.91099</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nine Months Journal</t>
+          <t>A-Journal Notebook Checkered Pink</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MYJ.19007</t>
+          <t>MYJ.91101</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kitchen Journal</t>
+          <t>A-Journal Notebook A7 Lines Thin</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MYJ.19008</t>
+          <t>MYJ.91102</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Notebook - Lilac</t>
+          <t>A-Journal One Line a Day - Toile de Jouy - Blue</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D89" s="2" t="n"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>MYJ.25021</t>
+          <t>MYJ.91104</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>A-Journal Monthly Journal Diary</t>
+          <t>Sketchbook A4 Circle Pink Red</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MYJ.91029</t>
+          <t>MYJ.91105</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>A-Journal Address Book</t>
+          <t>A-Journal One line a day - Flow blue</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MYJ.91030</t>
+          <t>MYJ.91106</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Daily Journal</t>
+          <t>A-Journal One Line a Day - Lavender Stripes</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MYJ.91034</t>
+          <t>MYJ.91110</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>A-Journal Deskplanner - Linen</t>
+          <t>Birthday Calendar Arty 2.0</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MYJ.91035</t>
+          <t>MYJ.91113</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>A-Journal Gespreksstarter - Gesprekskaarten (Nederlands/Dutch)</t>
+          <t>A-Journal Notebook Toile de Jouy - Green</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MYJ.91036</t>
+          <t>MYJ.91115</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>A-Journal Notebook - Beige</t>
+          <t>A-Block A5 - Blank</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>MYJ.91042</t>
+          <t>MYJ.91118</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>A-Journal Set of 2 Envelop Folders</t>
+          <t>A-Journal Notepad Flow Mint</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MYJ.91045</t>
+          <t>MYJ.91121</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Writing Paper</t>
+          <t>A-Journal Puzzle Apéro - 500 Pieces</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D97" s="2" t="n"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MYJ.91047</t>
+          <t>MYJ.91124</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>A-Journal Notepad - Blue</t>
+          <t>A-Journal Password Journal - Stripes Blue</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MYJ.91048</t>
+          <t>MYJ.91125</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>A-Journal Notepad - Red</t>
+          <t>A-Journal Password Journal Checkered</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v>1</v>
       </c>
+      <c r="D99" s="2" t="n"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MYJ.91049</t>
+          <t>MYJ.91129</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>One Line A Day Journal Orange</t>
+          <t>A-Journal Notebook Cherry Red</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MYJ.91050</t>
+          <t>MYJ.91133</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Notebook Toile de Jouy</t>
+          <t>A-Journal Address Book - Stripes</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="D101" s="2" t="n"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MYJ.91051</t>
+          <t>MYJ.91142</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>A-Journal Undated Agenda</t>
+          <t>A-Journal Bullet Journal Abstract Pink</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v>2</v>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MYJ.91052</t>
+          <t>MYJ.91143</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>A-Journal Spiral Notebook - A4</t>
+          <t>A-Journal Bullet Journal Pink Bordeaux</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MYJ.91053</t>
+          <t>MYJ.91144</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>A-Journal Spiral Notebook - A5</t>
+          <t>A-Journal Notebook Pink</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MYJ.91056</t>
+          <t>MYJ.91147</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>A-Journal Notebook - Emerald Green</t>
+          <t>A-Journal Fruity Birthday Calendar</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D105" s="2" t="n"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MYJ.91058</t>
+          <t>MYJ.91168</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>A-Journal Notebook - Checkered Red</t>
+          <t>Intentions and Reflections Journal</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v>3</v>
       </c>
+      <c r="D106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MYJ.91059</t>
+          <t>MYJ.91180</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>A-Journal One Line a Day - Flow Mint</t>
+          <t>A-Yatzy Green</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>MYJ.91060</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>A-Journal Set of 2 Softcover Notebooks - Coral + Lilac</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>MYJ.91061</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>A-Journal Notepad - Beige</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>MYJ.91064</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>A-Journal Birthday Calender - Arty</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>MYJ.91065</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Keycord long - Lavender Blue - 45 cm</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>MYJ.91067</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Groovy - Pink</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>MYJ.91069</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook - Flow Mint</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>MYJ.91070</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook - Checkered Lavender</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>MYJ.91073</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>A-Puzzle Pool Party</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>MYJ.91074</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>A-Puzzle Tropical</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>MYJ.91076</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>A-Journal Journaling Cards</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>MYJ.91077</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>A-Journal One Line a Day Checkered</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>MYJ.91080</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>A-Journal One Line a Day - Circle</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>MYJ.91081</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Terracotta Checkered</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>MYJ.91083</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>A-Journal Playing Cards - Green</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>MYJ.91084</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>A-Journal Affirmation Cards - Daily Affirmations</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>MYJ.91087</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>A-Journal A6 Notebook - Pink</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>MYJ.91088</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>A-Journal A6 Notebook - Green Stripes</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>MYJ.91089</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>A-Journal A6 Notebook - Dark Green</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>MYJ.91090</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>A-Journal A6 Notebook - Coral Flowers</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>MYJ.91091</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>A-Journal Spiral Deskplanner - Checkered</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>MYJ.91093</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>A-Journal A5 Notebook Spiral Flow</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>MYJ.91094</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>A-Journal Accordion Folder - Coral</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>MYJ.91095</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>A-Journal One Line a Day - Linen Emerald</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>MYJ.91096</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>One Line a Day Flow - Blue Brown</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>MYJ.91097</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Arty Green</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>MYJ.91098</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Collage Pink</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>MYJ.91099</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Checkered Pink</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>MYJ.91100</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook A7 Checkered Thin</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>MYJ.91101</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook A7 Lines Thin</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>MYJ.91102</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>A-Journal One Line a Day - Toile de Jouy - Blue</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>MYJ.91103</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Sketchbook A4 Flow Coral</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>MYJ.91104</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Sketchbook A4 Circle Pink Red</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>MYJ.91105</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>A-Journal One line a day - Flow blue</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>MYJ.91106</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>A-Journal One Line a Day - Lavender Stripes</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>MYJ.91110</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Birthday Calendar Arty 2.0</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>MYJ.91111</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>A-Journal Notepad Toile de Jouy Green</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>MYJ.91113</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Toile de Jouy - Green</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>MYJ.91115</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>A-Block A5 - Blank</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>MYJ.91118</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>A-Journal Notepad Flow Mint</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>MYJ.91121</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>A-Journal Puzzle Apéro - 500 Pieces</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>MYJ.91123</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>A-Journal A6 Notebook Checkered</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>MYJ.91124</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>A-Journal Password Journal - Stripes Blue</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>MYJ.91125</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>A-Journal Password Journal Checkered</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>MYJ.91126</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>A-Journal x Curiositeas One line a day</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>MYJ.91127</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>A-Journal x Curiositeas Notebook</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>MYJ.91128</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>A-Journal x Curiositeas Set of 2 notebooks</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>MYJ.91129</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Cherry Red</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>MYJ.91131</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>A-Journal Keycord - Short - Red</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>MYJ.91132</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>A-Journal Keycord - Long - Pink</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>MYJ.91133</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>A-Journal Address Book - Stripes</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>MYJ.91141</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Dark Blue</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>MYJ.91142</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>A-Journal Bullet Journal Abstract Pink</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>MYJ.91143</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>A-Journal Bullet Journal Pink Bordeaux</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>MYJ.91144</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Pink</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>MYJ.91145</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>A-Yatzy Refill Pink Red</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>MYJ.91146</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>A-Yatzy Refill Blue</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>MYJ.91147</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>A-Journal Fruity Birthday Calendar</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>MYJ.91149</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>A-Journal Playing Cards - Circus</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>MYJ.91150</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>A-Journal Conversation Cards</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>MYJ.91151</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>A-Puzzle Mini - Circus</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>MYJ.91152</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>A-Journal Birthday Calendar - Circus</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>MYJ.91154</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>A-Journal Pencils - Yellow box</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>MYJ.91155</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>A-Journal Pencils - Red Box</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>MYJ.91156</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>A-Journal Pencils - Blue box</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>MYJ.91159</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>A-Journal Pen - Red Blue</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>MYJ.91160</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>A-Journal Pen - Orange Blue</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>MYJ.91161</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>A-Journal Pen - Coral Bordeaux</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>MYJ.91162</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>A-Journal Notepad Pink Checkered</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>MYJ.91163</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>A-Journal Notepad Dark Blue Light Blue</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>MYJ.91166</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Modernist Pink Red</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>MYJ.91167</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>A-Journal Notebook Thin Checkered Pink Red</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>MYJ.91168</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Intentions and Reflections Journal</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>MYJ.91169</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Personal Journal Stripes Blue</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>MYJ.91173</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>A-Journal A7 Notitieboek - Delft Blue</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>MYJ.91175</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>A-Journal Notepad - Delft Blue</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>MYJ.91176</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>A-Journal A7 Notebook - Red</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>MYJ.91177</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>A-Journal A7 Notebook - Mint Green</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>MYJ.91179</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>A-Journal x Marie Marie Notepad</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>MYJ.91180</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>A-Yatzy Green</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>PP.91002</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Baby's First Year</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="n">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C187"/>
+  <autoFilter ref="A1:D107"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3250,77 +2267,1574 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Naam</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Qty op lijst</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Al besteld (EFS)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MYJ.27023</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>A-Planner Diary 2027 - Beige Linen</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331627: 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>MYJ.27024</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>A-Planner Diary 2027 - Pink Linen</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331627: 18, 1335669: 144</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FAB.91212</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Fabrique Notebook - Happy Flowers</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FAB.91228</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>One Line a Day Sun</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1331627: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FAB.91231</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fabrique Notebook - Sun Beige Lavender</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FAB.91233</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fabrique Notebook - Sun Pink</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1331627: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FAB.91237</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fabrique A6 Notebook - Stripes</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1335669: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FAB.91242</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fabrique Sketchbook A4 Sun</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1331627: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FAB.91250</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Birthday Calendar - Flower Vase</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FAB.91253</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fabrique Playing Cards Stripes - Red Pink</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FAB.91255</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Fabrique Writing Cards</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1319950: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FAB.91262</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Fabrique Notepad Paris</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FAB.91264</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fabrique Meal planner A Table</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1331627: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FAB.91266</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>One line a day Stripes Pink Red</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331627: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FAB.91267</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Notepad Stripes Pink Red</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1331627: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FAB.91273</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Fabrique Playing Cards - Dogs</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331627: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FAB.91274</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Fabrique Playing  Cards - Cats</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331627: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FAB.91277</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Fabrique Puzzle Mini - Dogs+Cats</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331627: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FAB.91279</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Fabrique Cardset Dogs+Cats</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FAB.91280</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fabrique Recipe Journal - A Table</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FAB.91281</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Fabrique Notebook Print Multi</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FAB.91282</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Fabrique Notebook Flowers Blue</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>MYJ.25021</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>A-Journal Monthly Journal Diary</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>MYJ.91035</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>A-Journal Gespreksstarter - Gesprekskaarten (Nederlands/Dutch)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MYJ.91036</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>A-Journal Notebook - Beige</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MYJ.91042</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>A-Journal Set of 2 Envelop Folders</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>MYJ.91048</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>A-Journal Notepad - Red</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1319950: 2, 1331192: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>MYJ.91049</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>One Line A Day Journal Orange</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331627: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>MYJ.91053</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>A-Journal Spiral Notebook - A5</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>MYJ.91056</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>A-Journal Notebook - Emerald Green</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>MYJ.91058</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>A-Journal Notebook - Checkered Red</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1331627: 36</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>MYJ.91065</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Keycord long - Lavender Blue - 45 cm</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1331627: 1, 1335669: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>MYJ.91070</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>A-Journal Notebook - Checkered Lavender</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1331627: 37</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>MYJ.91080</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A-Journal One Line a Day - Circle</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>MYJ.91083</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A-Journal Playing Cards - Green</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MYJ.91091</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A-Journal Spiral Deskplanner - Checkered</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>MYJ.91093</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A-Journal A5 Notebook Spiral Flow</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1319950: 2, 1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MYJ.91098</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A-Journal Notebook Collage Pink</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MYJ.91100</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A-Journal Notebook A7 Checkered Thin</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1319950: 2, 1331627: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MYJ.91103</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Sketchbook A4 Flow Coral</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1331627: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MYJ.91111</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A-Journal Notepad Toile de Jouy Green</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MYJ.91123</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A-Journal A6 Notebook Checkered</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1331627: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MYJ.91141</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A-Journal Notebook Dark Blue</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331627: 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>MYJ.91149</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A-Journal Playing Cards - Circus</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>MYJ.91150</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>A-Journal Conversation Cards</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331192: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>MYJ.91151</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A-Puzzle Mini - Circus</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MYJ.91152</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A-Journal Birthday Calendar - Circus</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>MYJ.91154</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A-Journal Pencils - Yellow box</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331192: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>MYJ.91155</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>A-Journal Pencils - Red Box</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331192: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>MYJ.91156</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>A-Journal Pencils - Blue box</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331192: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>MYJ.91159</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>A-Journal Pen - Red Blue</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1335669: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MYJ.91160</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>A-Journal Pen - Orange Blue</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331192: 1, 1335669: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MYJ.91161</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A-Journal Pen - Coral Bordeaux</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331192: 1, 1335669: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MYJ.91162</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>A-Journal Notepad Pink Checkered</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>MYJ.91163</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A-Journal Notepad Dark Blue Light Blue</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>MYJ.91166</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A-Journal Notebook Modernist Pink Red</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>MYJ.91167</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A-Journal Notebook Thin Checkered Pink Red</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>MYJ.91169</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Personal Journal Stripes Blue</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>MYJ.91173</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>A-Journal A7 Notitieboek - Delft Blue</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1319950: 3, 1331192: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>MYJ.91175</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>A-Journal Notepad - Delft Blue</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MYJ.91176</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A-Journal A7 Notebook - Red</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MYJ.91177</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A-Journal A7 Notebook - Mint Green</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1319950: 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MYJ.91179</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A-Journal x Marie Marie Notepad</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1331192: 2, 1335669: 3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="130" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Samenstelling aanvullijst beurs (5 oktober 2026)</t>
+          <t>Aanvullijst beurs v2 (5 oktober 2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Samples</t>
+          <t>Basis</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29 producten met het aantal van a-journal.github.io/beurssamples-styling (ook als ze in de telling al op 3 staan)</t>
+          <t>de lijst van Maurits van 5 oktober: 169 regels, 841 stuks</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aanvulling uit telling</t>
+          <t>Al besteld</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>157 producten uit "Telling 01-10-2026 11:32" (wholesale) die onder de 3 zaten; qty = 3 min geteld</t>
+          <t>EFS-orders 1331627 (8 sep), 1335669 (18 sep), 1331192 (7 sep) en 1319950 (10 aug), allemaal status verzonden; order 1337588 (23 sep) is geannuleerd en telt niet mee</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Weggelaten</t>
+          <t>Regel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026/2027-producten (SKU .26xxx/.27xxx) en de SKU's die in de telling als uitgesloten staan</t>
+          <t>Qty = lijst min al besteld; een regel valt weg als er al evenveel of meer besteld is (tabblad Weggehaald)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Overlap</t>
+          <t>Verpakkingen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22 sample-SKU's zaten ook in de aanvulling; die staan één keer, met het sample-aantal: MYJ.91136, MYJ.91032, MYJ.91044, MYJ.91057, MYJ.91082, MYJ.91165, MYJ.91130, MYJ.91078, MYJ.91135, MYJ.91079, MYJ.91157, MYJ.91158, MYJ.91075, MYJ.91134, MYJ.91140, MYJ.91139, FAB.91220, FAB.91251, FAB.91252, FAB.91278, MYJ.91040, FAB.91235</t>
+          <t>EFS-regels met .innerbox18 tellen als 18 stuks, .innerbox als het aantal uit de productnaam (36)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Totaal</t>
+          <t>Resultaat</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>186 regels, 741 stuks</t>
+          <t>106 regels, 561 stuks; 63 regels weggehaald</t>
         </is>
       </c>
     </row>
